--- a/reportes/insumos.xlsx
+++ b/reportes/insumos.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,30 +424,53 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>tela guanenta</v>
+        <v>presentacion</v>
       </c>
       <c r="B2" t="str">
         <v>Telas</v>
       </c>
       <c r="C2" t="str">
-        <v>rollos</v>
+        <v>unidades</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="G2">
         <v>800000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>tela guanenta</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Telas</v>
+      </c>
+      <c r="C3" t="str">
+        <v>rollos</v>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>200000</v>
+      </c>
+      <c r="G3">
+        <v>2800000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>